--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9eb25f887a4847dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R540ad5970df74de1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R70ffefa2cdaf490b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R22b40bfc31b3488c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rcd8364daeb82449d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R6d83debe2c0940db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R442193ad5e7945df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R0ebacc9e80b24143"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rea4e3c9557ff44e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R8eef5f38489a4aaf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -739,7 +739,7 @@
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>reference_members</x:v>
+        <x:v>delivery_paths</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
         <x:v>output/src/triage_csp_reports.mjs,output/reports/normalized_violations.csv,output/reports/source_lookup.csv,output/reports/suppressed_reports.csv,output/reports/alert_rollup.csv</x:v>
@@ -748,7 +748,7 @@
         <x:v>相对路径逐字匹配</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>reference.zip成员</x:v>
+        <x:v>Prompt声明的业务交付路径</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
